--- a/fx/2026/march/trading_journal_march_2026.xlsx
+++ b/fx/2026/march/trading_journal_march_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsetiyawan\Documents\Self Projects\trading_journal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsetiyawan\Documents\Self Projects\trading_journal\daily_pnl\fx\2026\march\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39922CBB-61F7-4634-890E-0E5C8C758065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018A9D5C-E745-4033-9EB6-4A51EC44C5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{9451B767-0217-457C-A658-57F96A9B9C5B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9451B767-0217-457C-A658-57F96A9B9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="70">
   <si>
     <t>L</t>
   </si>
@@ -251,6 +251,27 @@
   </si>
   <si>
     <t>Berada di area supply, namun tidak sesuai dengan data dari news</t>
+  </si>
+  <si>
+    <t>US30</t>
+  </si>
+  <si>
+    <t>Berada di area supply, namun buying masih kuat</t>
+  </si>
+  <si>
+    <t>Entry gegabah</t>
+  </si>
+  <si>
+    <t>Harga baru tembus resis, kemudian retrace, memanfaatkan tf 5 menit</t>
+  </si>
+  <si>
+    <t>Harga berada di area demand zone, di minor tf 5 menit</t>
+  </si>
+  <si>
+    <t>Harga berada di area support become resistance di tf 1 jam</t>
+  </si>
+  <si>
+    <t>Harga berada di area support become resistance &amp; trendline di tf 1 jam</t>
   </si>
 </sst>
 </file>
@@ -891,10 +912,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>12</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1117,10 +1138,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$27:$N$51</c:f>
+              <c:f>Sheet1!$N$27:$N$52</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0.15756422971960665</c:v>
                 </c:pt>
@@ -1180,6 +1201,24 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.69526587311577448</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.64854782762339935</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.64854782762339935</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.84994355092851281</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.87954804739463555</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.88621779310156523</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.88376748690489426</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1498,9 +1537,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$R$9:$R$18</c:f>
+              <c:f>Sheet1!$R$9:$R$19</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>USTEC</c:v>
                 </c:pt>
@@ -1531,15 +1570,18 @@
                 <c:pt idx="9">
                   <c:v>EURJPY</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>US30</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$S$9:$S$18</c:f>
+              <c:f>Sheet1!$S$9:$S$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1547,16 +1589,16 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-1</c:v>
@@ -1568,6 +1610,9 @@
                   <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3934,7 +3979,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="50">
         <f>SUMIF(K27:K52,"L",L27:L52)</f>
-        <v>-625861.54</v>
+        <v>-676718.74</v>
       </c>
       <c r="J5" s="51"/>
       <c r="K5" s="51"/>
@@ -3949,7 +3994,7 @@
       </c>
       <c r="S5" s="19">
         <f>COUNTIF(K27:K1048576,"W")</f>
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -3975,7 +4020,7 @@
       </c>
       <c r="S6" s="19">
         <f>COUNTIF(K27:K1048576,"L")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -4046,7 +4091,7 @@
         <v>USTEC</v>
       </c>
       <c r="S9" s="19" cm="1">
-        <f t="array" ref="S9:S18">SUMIF(D27:D52,R9:R18,R27:R52)</f>
+        <f t="array" ref="S9:S19">SUMIF(D27:D52,R9:R19,R27:R52)</f>
         <v>1</v>
       </c>
     </row>
@@ -4085,7 +4130,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="50">
         <f>SUMIF(K27:K52,"W",L27:L52)</f>
-        <v>1345008.5999999999</v>
+        <v>1590842.12</v>
       </c>
       <c r="J11" s="51"/>
       <c r="K11" s="51"/>
@@ -4099,7 +4144,7 @@
         <v>EURUSD</v>
       </c>
       <c r="S11" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -4128,19 +4173,19 @@
         <v>DE30</v>
       </c>
       <c r="S12" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="39">
         <f>I11+I5</f>
-        <v>719147.05999999982</v>
+        <v>914123.38000000012</v>
       </c>
       <c r="C13" s="40"/>
       <c r="D13" s="39">
         <f>D4+B13</f>
-        <v>1753495.3399999999</v>
+        <v>1948471.6600000001</v>
       </c>
       <c r="E13" s="40"/>
       <c r="F13" s="1"/>
@@ -4184,7 +4229,7 @@
         <v>GBPUSD</v>
       </c>
       <c r="S14" s="19">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -4311,7 +4356,10 @@
         <f>O45-O35</f>
         <v>155382.66999999969</v>
       </c>
-      <c r="L18" s="9"/>
+      <c r="L18" s="18">
+        <f>O52-O45</f>
+        <v>187301.26000000024</v>
+      </c>
       <c r="M18"/>
       <c r="N18"/>
       <c r="O18"/>
@@ -4362,8 +4410,11 @@
       <c r="O19"/>
       <c r="P19"/>
       <c r="Q19" s="4"/>
-      <c r="R19" s="19">
-        <v>0</v>
+      <c r="R19" s="19" t="str">
+        <v>US30</v>
+      </c>
+      <c r="S19" s="19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5534,7 +5585,7 @@
         <v>1282.4100000000001</v>
       </c>
       <c r="M45" s="8">
-        <f t="shared" ref="M45:M46" si="35">(L45/$D$4)</f>
+        <f t="shared" ref="M45" si="35">(L45/$D$4)</f>
         <v>1.2398241721830871E-3</v>
       </c>
       <c r="N45" s="8">
@@ -5555,6 +5606,7 @@
       </c>
     </row>
     <row r="46" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
       <c r="B46" s="1">
         <v>19</v>
       </c>
@@ -5586,7 +5638,7 @@
         <v>-7675.06</v>
       </c>
       <c r="M46" s="8">
-        <f t="shared" ref="M46" si="38">(L46/$D$4)</f>
+        <f t="shared" ref="M46:M47" si="38">(L46/$D$4)</f>
         <v>-7.4201892615899162E-3</v>
       </c>
       <c r="N46" s="8">
@@ -5600,51 +5652,328 @@
       <c r="P46" s="15" t="s">
         <v>62</v>
       </c>
+      <c r="Q46" s="4"/>
       <c r="R46" s="19">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P47" s="15"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="1">
+        <v>20</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="6">
+        <v>5184.3490000000002</v>
+      </c>
+      <c r="G47" s="6">
+        <v>5187.2110000000002</v>
+      </c>
+      <c r="H47" s="6">
+        <v>5064.3729999999996</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="L47" s="6">
+        <v>-48322.73</v>
+      </c>
+      <c r="M47" s="8">
+        <f t="shared" ref="M47:M48" si="41">(L47/$D$4)</f>
+        <v>-4.6718045492375161E-2</v>
+      </c>
+      <c r="N47" s="8">
+        <f t="shared" ref="N47" si="42">(O47-$D$4)/$D$4</f>
+        <v>0.64854782762339935</v>
+      </c>
+      <c r="O47" s="6">
+        <f t="shared" ref="O47" si="43">O46+L47</f>
+        <v>1705172.6099999996</v>
+      </c>
+      <c r="P47" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q47" s="4"/>
       <c r="R47" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P48" s="15"/>
+      <c r="A48" s="4"/>
+      <c r="B48" s="1">
+        <v>21</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="6">
+        <v>23966.1</v>
+      </c>
+      <c r="G48" s="6">
+        <v>24138.3</v>
+      </c>
+      <c r="H48" s="6">
+        <v>23695.7</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="6">
+        <v>0</v>
+      </c>
+      <c r="M48" s="8">
+        <f t="shared" ref="M48:M49" si="44">(L48/$D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="N48" s="8">
+        <f t="shared" ref="N48" si="45">(O48-$D$4)/$D$4</f>
+        <v>0.64854782762339935</v>
+      </c>
+      <c r="O48" s="6">
+        <f t="shared" ref="O48" si="46">O47+L48</f>
+        <v>1705172.6099999996</v>
+      </c>
+      <c r="P48" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q48" s="4"/>
       <c r="R48" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="49" spans="16:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P49" s="15"/>
+    <row r="49" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="B49" s="1">
+        <v>22</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F49" s="6">
+        <v>5197.3789999999999</v>
+      </c>
+      <c r="G49" s="6">
+        <v>5188.3130000000001</v>
+      </c>
+      <c r="H49" s="6">
+        <v>5209.7610000000004</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="6">
+        <v>208313.32</v>
+      </c>
+      <c r="M49" s="8">
+        <f t="shared" ref="M49:M50" si="47">(L49/$D$4)</f>
+        <v>0.20139572330511343</v>
+      </c>
+      <c r="N49" s="8">
+        <f t="shared" ref="N49" si="48">(O49-$D$4)/$D$4</f>
+        <v>0.84994355092851281</v>
+      </c>
+      <c r="O49" s="6">
+        <f t="shared" ref="O49" si="49">O48+L49</f>
+        <v>1913485.9299999997</v>
+      </c>
+      <c r="P49" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q49" s="4"/>
       <c r="R49" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="50" spans="16:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P50" s="15"/>
+    <row r="50" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" s="1">
+        <v>22</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F50" s="6">
+        <v>47542.2</v>
+      </c>
+      <c r="G50" s="6">
+        <v>47462</v>
+      </c>
+      <c r="H50" s="6">
+        <v>47723.7</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="6">
+        <v>30621.360000000001</v>
+      </c>
+      <c r="M50" s="8">
+        <f t="shared" ref="M50:M51" si="50">(L50/$D$4)</f>
+        <v>2.960449646612261E-2</v>
+      </c>
+      <c r="N50" s="8">
+        <f t="shared" ref="N50" si="51">(O50-$D$4)/$D$4</f>
+        <v>0.87954804739463555</v>
+      </c>
+      <c r="O50" s="6">
+        <f t="shared" ref="O50" si="52">O49+L50</f>
+        <v>1944107.2899999998</v>
+      </c>
+      <c r="P50" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q50" s="4"/>
       <c r="R50" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="51" spans="16:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P51" s="15"/>
+    <row r="51" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="B51" s="1">
+        <v>23</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" s="6">
+        <v>1.3462700000000001</v>
+      </c>
+      <c r="G51" s="6">
+        <v>1.3469899999999999</v>
+      </c>
+      <c r="H51" s="6">
+        <v>1.34135</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="6">
+        <v>6898.84</v>
+      </c>
+      <c r="M51" s="8">
+        <f t="shared" ref="M51:M52" si="53">(L51/$D$4)</f>
+        <v>6.6697457069295847E-3</v>
+      </c>
+      <c r="N51" s="8">
+        <f t="shared" ref="N51" si="54">(O51-$D$4)/$D$4</f>
+        <v>0.88621779310156523</v>
+      </c>
+      <c r="O51" s="6">
+        <f t="shared" ref="O51" si="55">O50+L51</f>
+        <v>1951006.13</v>
+      </c>
+      <c r="P51" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q51" s="4"/>
       <c r="R51" s="19">
         <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4"/>
+      <c r="B52" s="1">
+        <v>24</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F52" s="6">
+        <v>1.16411</v>
+      </c>
+      <c r="G52" s="6">
+        <v>1.1653199999999999</v>
+      </c>
+      <c r="H52" s="6">
+        <v>1.1607099999999999</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K52" s="17" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="16:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P52" s="15"/>
+      <c r="L52" s="6">
+        <v>-2534.4699999999998</v>
+      </c>
+      <c r="M52" s="8">
+        <f t="shared" ref="M52" si="56">(L52/$D$4)</f>
+        <v>-2.4503061966710087E-3</v>
+      </c>
+      <c r="N52" s="8">
+        <f t="shared" ref="N52" si="57">(O52-$D$4)/$D$4</f>
+        <v>0.88376748690489426</v>
+      </c>
+      <c r="O52" s="6">
+        <f t="shared" ref="O52" si="58">O51+L52</f>
+        <v>1948471.66</v>
+      </c>
+      <c r="P52" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q52" s="4"/>
       <c r="R52" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/fx/2026/march/trading_journal_march_2026.xlsx
+++ b/fx/2026/march/trading_journal_march_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsetiyawan\Documents\Self Projects\trading_journal\daily_pnl\fx\2026\march\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018A9D5C-E745-4033-9EB6-4A51EC44C5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB7AEB2-5E72-4C71-A0A4-943BF2AA64AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9451B767-0217-457C-A658-57F96A9B9C5B}"/>
+    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{9451B767-0217-457C-A658-57F96A9B9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="75">
   <si>
     <t>L</t>
   </si>
@@ -272,6 +272,21 @@
   </si>
   <si>
     <t>Harga berada di area support become resistance &amp; trendline di tf 1 jam</t>
+  </si>
+  <si>
+    <t>11 Maret 2026</t>
+  </si>
+  <si>
+    <t>CHFJPY</t>
+  </si>
+  <si>
+    <t>Harga berada di area resistance, namun belum valid</t>
+  </si>
+  <si>
+    <t>Scalping menggunakan ichimoku</t>
+  </si>
+  <si>
+    <t>Harga berada di area resistance, namun pergerakan lama</t>
   </si>
 </sst>
 </file>
@@ -346,7 +361,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -555,7 +570,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -607,7 +622,6 @@
     <xf numFmtId="43" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -716,6 +730,10 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -912,10 +930,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>16</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1138,10 +1156,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$27:$N$52</c:f>
+              <c:f>Sheet1!$N$27:$N$60</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0.15756422971960665</c:v>
                 </c:pt>
@@ -1219,6 +1237,18 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.88376748690489426</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.81998042284171424</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.84082520057944099</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.8903491965008149</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.90821408819860938</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1537,9 +1567,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$R$9:$R$19</c:f>
+              <c:f>Sheet1!$R$9:$R$20</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>USTEC</c:v>
                 </c:pt>
@@ -1573,15 +1603,18 @@
                 <c:pt idx="10">
                   <c:v>US30</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>CHFJPY</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$S$9:$S$19</c:f>
+              <c:f>Sheet1!$S$9:$S$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1614,6 +1647,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3866,7 +3902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76C93DEB-C22F-4A44-AFA4-61A1DDE6BE07}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" customWidth="1"/>
@@ -3880,48 +3916,48 @@
     <col min="15" max="15" width="14.85546875" style="6" customWidth="1"/>
     <col min="16" max="16" width="69.85546875" style="1" customWidth="1"/>
     <col min="17" max="17" width="1.42578125" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="19"/>
-    <col min="19" max="19" width="9.140625" style="19" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="56"/>
+    <col min="19" max="19" width="9.140625" style="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
       <c r="Q1" s="4"/>
     </row>
     <row r="2" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
       <c r="Q2" s="4"/>
     </row>
     <row r="3" spans="1:19" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -3939,88 +3975,88 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="29">
+      <c r="C4" s="26"/>
+      <c r="D4" s="28">
         <v>1034348.28</v>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="49"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="48"/>
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4"/>
       <c r="P4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="19" t="s">
+      <c r="R4" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="S4" s="19" t="s">
+      <c r="S4" s="56" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="32"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="50">
+      <c r="I5" s="49">
         <f>SUMIF(K27:K52,"L",L27:L52)</f>
         <v>-676718.74</v>
       </c>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="52"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="51"/>
       <c r="M5"/>
       <c r="N5"/>
       <c r="O5"/>
       <c r="P5"/>
       <c r="Q5" s="4"/>
-      <c r="R5" s="19" t="s">
+      <c r="R5" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="S5" s="19">
+      <c r="S5" s="56">
         <f>COUNTIF(K27:K1048576,"W")</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="34"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="52"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="51"/>
       <c r="M6"/>
       <c r="N6"/>
       <c r="O6"/>
       <c r="P6"/>
       <c r="Q6" s="4"/>
-      <c r="R6" s="19" t="s">
+      <c r="R6" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="S6" s="19">
+      <c r="S6" s="56">
         <f>COUNTIF(K27:K1048576,"L")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -4029,10 +4065,10 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="52"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="51"/>
       <c r="M7"/>
       <c r="N7"/>
       <c r="O7"/>
@@ -4041,42 +4077,42 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="55"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="54"/>
       <c r="M8"/>
       <c r="N8"/>
       <c r="O8"/>
       <c r="P8"/>
       <c r="Q8" s="4"/>
-      <c r="R8" s="19" t="s">
+      <c r="R8" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="19" t="s">
+      <c r="S8" s="56" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="35">
+      <c r="B9" s="34">
         <v>0.05</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="39">
+      <c r="C9" s="35"/>
+      <c r="D9" s="38">
         <f>D4*B9</f>
         <v>51717.414000000004</v>
       </c>
-      <c r="E9" s="40"/>
+      <c r="E9" s="39"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -4086,39 +4122,39 @@
       <c r="O9"/>
       <c r="P9"/>
       <c r="Q9" s="4"/>
-      <c r="R9" s="19" t="str" cm="1">
-        <f t="array" ref="R9:R19">_xlfn.UNIQUE(D27:D52)</f>
+      <c r="R9" s="56" t="str" cm="1">
+        <f t="array" ref="R9:R21">_xlfn.UNIQUE(D27:D60)</f>
         <v>USTEC</v>
       </c>
-      <c r="S9" s="19" cm="1">
-        <f t="array" ref="S9:S19">SUMIF(D27:D52,R9:R19,R27:R52)</f>
+      <c r="S9" s="56" cm="1">
+        <f t="array" ref="S9:S21">SUMIF(D27:D52,R9:R21,R27:R52)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="47" t="s">
+      <c r="I10" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="49"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="48"/>
       <c r="M10"/>
       <c r="N10"/>
       <c r="O10"/>
       <c r="P10"/>
       <c r="Q10" s="4"/>
-      <c r="R10" s="19" t="str">
+      <c r="R10" s="56" t="str">
         <v>JP225</v>
       </c>
-      <c r="S10" s="19">
+      <c r="S10" s="56">
         <v>2</v>
       </c>
     </row>
@@ -4128,107 +4164,107 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="I11" s="50">
+      <c r="I11" s="49">
         <f>SUMIF(K27:K52,"W",L27:L52)</f>
         <v>1590842.12</v>
       </c>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="52"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="51"/>
       <c r="M11"/>
       <c r="N11"/>
       <c r="O11"/>
       <c r="P11"/>
       <c r="Q11" s="4"/>
-      <c r="R11" s="19" t="str">
+      <c r="R11" s="56" t="str">
         <v>EURUSD</v>
       </c>
-      <c r="S11" s="19">
+      <c r="S11" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="43" t="s">
+      <c r="C12" s="45"/>
+      <c r="D12" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="44"/>
+      <c r="E12" s="43"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="52"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="51"/>
       <c r="M12"/>
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12"/>
       <c r="Q12" s="4"/>
-      <c r="R12" s="19" t="str">
+      <c r="R12" s="56" t="str">
         <v>DE30</v>
       </c>
-      <c r="S12" s="19">
+      <c r="S12" s="56">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="39">
+      <c r="B13" s="38">
         <f>I11+I5</f>
         <v>914123.38000000012</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="39">
+      <c r="C13" s="39"/>
+      <c r="D13" s="38">
         <f>D4+B13</f>
         <v>1948471.6600000001</v>
       </c>
-      <c r="E13" s="40"/>
+      <c r="E13" s="39"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="52"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="51"/>
       <c r="M13"/>
       <c r="N13"/>
       <c r="O13"/>
       <c r="P13"/>
       <c r="Q13" s="4"/>
-      <c r="R13" s="19" t="str">
+      <c r="R13" s="56" t="str">
         <v>XAUUSD</v>
       </c>
-      <c r="S13" s="19">
+      <c r="S13" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="42"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="55"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="54"/>
       <c r="M14"/>
       <c r="N14"/>
       <c r="O14"/>
       <c r="P14"/>
       <c r="Q14" s="4"/>
-      <c r="R14" s="19" t="str">
+      <c r="R14" s="56" t="str">
         <v>GBPUSD</v>
       </c>
-      <c r="S14" s="19">
+      <c r="S14" s="56">
         <v>0</v>
       </c>
     </row>
@@ -4244,10 +4280,10 @@
       <c r="O15"/>
       <c r="P15"/>
       <c r="Q15" s="4"/>
-      <c r="R15" s="19" t="str">
+      <c r="R15" s="56" t="str">
         <v>USDJPY</v>
       </c>
-      <c r="S15" s="19">
+      <c r="S15" s="56">
         <v>-1</v>
       </c>
     </row>
@@ -4269,10 +4305,10 @@
       <c r="O16"/>
       <c r="P16"/>
       <c r="Q16" s="4"/>
-      <c r="R16" s="19" t="str">
+      <c r="R16" s="56" t="str">
         <v>NZDUSD</v>
       </c>
-      <c r="S16" s="19">
+      <c r="S16" s="56">
         <v>2</v>
       </c>
     </row>
@@ -4314,10 +4350,10 @@
       <c r="O17"/>
       <c r="P17"/>
       <c r="Q17" s="4"/>
-      <c r="R17" s="19" t="str">
+      <c r="R17" s="56" t="str">
         <v>NZDJPY</v>
       </c>
-      <c r="S17" s="19">
+      <c r="S17" s="56">
         <v>-1</v>
       </c>
     </row>
@@ -4365,10 +4401,10 @@
       <c r="O18"/>
       <c r="P18"/>
       <c r="Q18" s="4"/>
-      <c r="R18" s="19" t="str">
+      <c r="R18" s="56" t="str">
         <v>EURJPY</v>
       </c>
-      <c r="S18" s="19">
+      <c r="S18" s="56">
         <v>1</v>
       </c>
     </row>
@@ -4410,17 +4446,20 @@
       <c r="O19"/>
       <c r="P19"/>
       <c r="Q19" s="4"/>
-      <c r="R19" s="19" t="str">
+      <c r="R19" s="56" t="str">
         <v>US30</v>
       </c>
-      <c r="S19" s="19">
+      <c r="S19" s="56">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
-      <c r="C20" s="10"/>
+      <c r="C20" s="55">
+        <f>O56-O52</f>
+        <v>25286.300000000047</v>
+      </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -4435,6 +4474,12 @@
       <c r="O20"/>
       <c r="P20"/>
       <c r="Q20" s="4"/>
+      <c r="R20" s="56" t="str">
+        <v>CHFJPY</v>
+      </c>
+      <c r="S20" s="56">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
@@ -4474,6 +4519,12 @@
       <c r="O21"/>
       <c r="P21"/>
       <c r="Q21" s="4"/>
+      <c r="R21" s="56">
+        <v>0</v>
+      </c>
+      <c r="S21" s="56">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
@@ -4500,17 +4551,17 @@
       <c r="C23" s="2">
         <v>31</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="23"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="22"/>
       <c r="M23"/>
       <c r="N23"/>
       <c r="O23"/>
@@ -4521,15 +4572,15 @@
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="26"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="25"/>
       <c r="M24"/>
       <c r="N24"/>
       <c r="O24"/>
@@ -4646,7 +4697,7 @@
         <v>26</v>
       </c>
       <c r="Q27" s="4"/>
-      <c r="R27" s="19">
+      <c r="R27" s="56">
         <f>IF(K27="W",1,IF(K27="L",-1,0))</f>
         <v>1</v>
       </c>
@@ -4699,8 +4750,8 @@
         <v>25</v>
       </c>
       <c r="Q28" s="4"/>
-      <c r="R28" s="19">
-        <f t="shared" ref="R28:R52" si="3">IF(K28="W",1,IF(K28="L",-1,0))</f>
+      <c r="R28" s="56">
+        <f t="shared" ref="R28:R60" si="3">IF(K28="W",1,IF(K28="L",-1,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -4752,7 +4803,7 @@
         <v>32</v>
       </c>
       <c r="Q29" s="4"/>
-      <c r="R29" s="19">
+      <c r="R29" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -4805,7 +4856,7 @@
         <v>37</v>
       </c>
       <c r="Q30" s="4"/>
-      <c r="R30" s="19">
+      <c r="R30" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -4858,7 +4909,7 @@
         <v>40</v>
       </c>
       <c r="Q31" s="4"/>
-      <c r="R31" s="19">
+      <c r="R31" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -4911,7 +4962,7 @@
         <v>43</v>
       </c>
       <c r="Q32" s="4"/>
-      <c r="R32" s="19">
+      <c r="R32" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -4964,7 +5015,7 @@
         <v>46</v>
       </c>
       <c r="Q33" s="4"/>
-      <c r="R33" s="19">
+      <c r="R33" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -5017,7 +5068,7 @@
         <v>49</v>
       </c>
       <c r="Q34" s="4"/>
-      <c r="R34" s="19">
+      <c r="R34" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -5070,7 +5121,7 @@
         <v>49</v>
       </c>
       <c r="Q35" s="4"/>
-      <c r="R35" s="19">
+      <c r="R35" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5123,7 +5174,7 @@
         <v>52</v>
       </c>
       <c r="Q36" s="4"/>
-      <c r="R36" s="19">
+      <c r="R36" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -5176,7 +5227,7 @@
         <v>53</v>
       </c>
       <c r="Q37" s="4"/>
-      <c r="R37" s="19">
+      <c r="R37" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5229,7 +5280,7 @@
         <v>51</v>
       </c>
       <c r="Q38" s="4"/>
-      <c r="R38" s="19">
+      <c r="R38" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5282,7 +5333,7 @@
         <v>57</v>
       </c>
       <c r="Q39" s="4"/>
-      <c r="R39" s="19">
+      <c r="R39" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5335,7 +5386,7 @@
         <v>57</v>
       </c>
       <c r="Q40" s="4"/>
-      <c r="R40" s="19">
+      <c r="R40" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -5388,7 +5439,7 @@
         <v>57</v>
       </c>
       <c r="Q41" s="4"/>
-      <c r="R41" s="19">
+      <c r="R41" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -5441,7 +5492,7 @@
         <v>57</v>
       </c>
       <c r="Q42" s="4"/>
-      <c r="R42" s="19">
+      <c r="R42" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -5494,7 +5545,7 @@
         <v>58</v>
       </c>
       <c r="Q43" s="4"/>
-      <c r="R43" s="19">
+      <c r="R43" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -5547,7 +5598,7 @@
         <v>59</v>
       </c>
       <c r="Q44" s="4"/>
-      <c r="R44" s="19">
+      <c r="R44" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5600,7 +5651,7 @@
         <v>60</v>
       </c>
       <c r="Q45" s="4"/>
-      <c r="R45" s="19">
+      <c r="R45" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5638,7 +5689,7 @@
         <v>-7675.06</v>
       </c>
       <c r="M46" s="8">
-        <f t="shared" ref="M46:M47" si="38">(L46/$D$4)</f>
+        <f t="shared" ref="M46" si="38">(L46/$D$4)</f>
         <v>-7.4201892615899162E-3</v>
       </c>
       <c r="N46" s="8">
@@ -5653,7 +5704,7 @@
         <v>62</v>
       </c>
       <c r="Q46" s="4"/>
-      <c r="R46" s="19">
+      <c r="R46" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -5691,7 +5742,7 @@
         <v>-48322.73</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" ref="M47:M48" si="41">(L47/$D$4)</f>
+        <f t="shared" ref="M47" si="41">(L47/$D$4)</f>
         <v>-4.6718045492375161E-2</v>
       </c>
       <c r="N47" s="8">
@@ -5706,7 +5757,7 @@
         <v>64</v>
       </c>
       <c r="Q47" s="4"/>
-      <c r="R47" s="19">
+      <c r="R47" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
@@ -5744,7 +5795,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="8">
-        <f t="shared" ref="M48:M49" si="44">(L48/$D$4)</f>
+        <f t="shared" ref="M48" si="44">(L48/$D$4)</f>
         <v>0</v>
       </c>
       <c r="N48" s="8">
@@ -5759,7 +5810,7 @@
         <v>65</v>
       </c>
       <c r="Q48" s="4"/>
-      <c r="R48" s="19">
+      <c r="R48" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5797,7 +5848,7 @@
         <v>208313.32</v>
       </c>
       <c r="M49" s="8">
-        <f t="shared" ref="M49:M50" si="47">(L49/$D$4)</f>
+        <f t="shared" ref="M49" si="47">(L49/$D$4)</f>
         <v>0.20139572330511343</v>
       </c>
       <c r="N49" s="8">
@@ -5812,7 +5863,7 @@
         <v>66</v>
       </c>
       <c r="Q49" s="4"/>
-      <c r="R49" s="19">
+      <c r="R49" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5850,7 +5901,7 @@
         <v>30621.360000000001</v>
       </c>
       <c r="M50" s="8">
-        <f t="shared" ref="M50:M51" si="50">(L50/$D$4)</f>
+        <f t="shared" ref="M50" si="50">(L50/$D$4)</f>
         <v>2.960449646612261E-2</v>
       </c>
       <c r="N50" s="8">
@@ -5865,7 +5916,7 @@
         <v>67</v>
       </c>
       <c r="Q50" s="4"/>
-      <c r="R50" s="19">
+      <c r="R50" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5903,7 +5954,7 @@
         <v>6898.84</v>
       </c>
       <c r="M51" s="8">
-        <f t="shared" ref="M51:M52" si="53">(L51/$D$4)</f>
+        <f t="shared" ref="M51" si="53">(L51/$D$4)</f>
         <v>6.6697457069295847E-3</v>
       </c>
       <c r="N51" s="8">
@@ -5918,7 +5969,7 @@
         <v>69</v>
       </c>
       <c r="Q51" s="4"/>
-      <c r="R51" s="19">
+      <c r="R51" s="56">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5956,7 +6007,7 @@
         <v>-2534.4699999999998</v>
       </c>
       <c r="M52" s="8">
-        <f t="shared" ref="M52" si="56">(L52/$D$4)</f>
+        <f t="shared" ref="M52:M53" si="56">(L52/$D$4)</f>
         <v>-2.4503061966710087E-3</v>
       </c>
       <c r="N52" s="8">
@@ -5971,9 +6022,253 @@
         <v>68</v>
       </c>
       <c r="Q52" s="4"/>
-      <c r="R52" s="19">
+      <c r="R52" s="56">
         <f t="shared" si="3"/>
         <v>-1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4"/>
+      <c r="B53" s="1">
+        <v>25</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53" s="6">
+        <v>203.40700000000001</v>
+      </c>
+      <c r="G53" s="6">
+        <v>204.02500000000001</v>
+      </c>
+      <c r="H53" s="6">
+        <v>202.649</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K53" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="L53" s="6">
+        <v>-65978.039999999994</v>
+      </c>
+      <c r="M53" s="8">
+        <f t="shared" ref="M53:M54" si="59">(L53/$D$4)</f>
+        <v>-6.3787064063179952E-2</v>
+      </c>
+      <c r="N53" s="8">
+        <f t="shared" ref="N53" si="60">(O53-$D$4)/$D$4</f>
+        <v>0.81998042284171424</v>
+      </c>
+      <c r="O53" s="6">
+        <f t="shared" ref="O53" si="61">O52+L53</f>
+        <v>1882493.6199999999</v>
+      </c>
+      <c r="P53" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="56">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4"/>
+      <c r="B54" s="1">
+        <v>26</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F54" s="6">
+        <v>5187.1760000000004</v>
+      </c>
+      <c r="G54" s="6">
+        <v>5179.2330000000002</v>
+      </c>
+      <c r="H54" s="6">
+        <v>5199.33</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="6">
+        <v>21560.76</v>
+      </c>
+      <c r="M54" s="8">
+        <f t="shared" ref="M54:M55" si="62">(L54/$D$4)</f>
+        <v>2.0844777737726791E-2</v>
+      </c>
+      <c r="N54" s="8">
+        <f t="shared" ref="N54" si="63">(O54-$D$4)/$D$4</f>
+        <v>0.84082520057944099</v>
+      </c>
+      <c r="O54" s="6">
+        <f t="shared" ref="O54" si="64">O53+L54</f>
+        <v>1904054.38</v>
+      </c>
+      <c r="P54" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="56">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4"/>
+      <c r="B55" s="1">
+        <v>27</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F55" s="6">
+        <v>5178.777</v>
+      </c>
+      <c r="G55" s="6">
+        <v>5182.3459999999995</v>
+      </c>
+      <c r="H55" s="6">
+        <v>5172.5069999999996</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="6">
+        <v>51225.06</v>
+      </c>
+      <c r="M55" s="8">
+        <f t="shared" ref="M55:M56" si="65">(L55/$D$4)</f>
+        <v>4.9523995921373791E-2</v>
+      </c>
+      <c r="N55" s="8">
+        <f t="shared" ref="N55" si="66">(O55-$D$4)/$D$4</f>
+        <v>0.8903491965008149</v>
+      </c>
+      <c r="O55" s="6">
+        <f t="shared" ref="O55" si="67">O54+L55</f>
+        <v>1955279.44</v>
+      </c>
+      <c r="P55" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="56">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4"/>
+      <c r="B56" s="1">
+        <v>28</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F56" s="6">
+        <v>203.58099999999999</v>
+      </c>
+      <c r="G56" s="6">
+        <v>203.88900000000001</v>
+      </c>
+      <c r="H56" s="6">
+        <v>202.626</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="6">
+        <v>18478.52</v>
+      </c>
+      <c r="M56" s="8">
+        <f t="shared" ref="M56" si="68">(L56/$D$4)</f>
+        <v>1.7864891697794479E-2</v>
+      </c>
+      <c r="N56" s="8">
+        <f t="shared" ref="N56" si="69">(O56-$D$4)/$D$4</f>
+        <v>0.90821408819860938</v>
+      </c>
+      <c r="O56" s="6">
+        <f t="shared" ref="O56" si="70">O55+L56</f>
+        <v>1973757.96</v>
+      </c>
+      <c r="P56" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="56">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="56">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
